--- a/out/엔젤로보틱스_리서치자료.xlsx
+++ b/out/엔젤로보틱스_리서치자료.xlsx
@@ -250,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -429,6 +429,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -795,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H45"/>
+  <dimension ref="B2:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -808,7 +811,6 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -839,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -1045,8 +1046,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1342,8 +1341,6 @@
       </c>
       <c r="E33" s="10" t="inlineStr"/>
     </row>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36">
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1379,7 +1376,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="B42" s="14" t="inlineStr">
         <is>
@@ -1414,18 +1410,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E36"/>
+  <dimension ref="A2:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1438,7 +1434,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>출처: 제10기 반기보고서 연혁, 리딩투자증권(2025.12.16)</t>
+          <t>1차 출처: 제10기 반기보고서(2026.06.30 기준) — 연혁, 지식재산권·인증현황, 사업의 내용, 예측치 대비 실적 괴리사유</t>
         </is>
       </c>
     </row>
@@ -1470,6 +1466,11 @@
           <t>현황</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>출처 (행별)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="63" t="inlineStr">
@@ -1484,12 +1485,17 @@
       </c>
       <c r="D7" s="53" t="inlineStr">
         <is>
-          <t>엔젤렉스 M20</t>
+          <t>엔젤렉스 M20 (M20-B-C3)</t>
         </is>
       </c>
       <c r="E7" s="53" t="inlineStr">
         <is>
           <t>2025.06 인증 획득</t>
+        </is>
+      </c>
+      <c r="F7" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁 「2025.06 엔젤렉스 M20 태국 TFDA 인증 획득」 + 인증현황 No.28</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1512,17 @@
       </c>
       <c r="D8" s="53" t="inlineStr">
         <is>
-          <t>엔젤렉스 M20 / angel SUIT H10</t>
+          <t>엔젤렉스 M20 (M20-A-C3, M20-B-C3)</t>
         </is>
       </c>
       <c r="E8" s="53" t="inlineStr">
         <is>
           <t>2025.07 인증 획득</t>
+        </is>
+      </c>
+      <c r="F8" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁 「2025.07 엔젤렉스 M20 베트남 보건복지부 인증 획득」 + 인증현황 No.29</t>
         </is>
       </c>
     </row>
@@ -1528,420 +1539,794 @@
       </c>
       <c r="D9" s="53" t="inlineStr">
         <is>
-          <t>엔젤렉스 M20</t>
+          <t>엔젤렉스 M20 (M20-A-C3, M20-B-C3)</t>
         </is>
       </c>
       <c r="E9" s="53" t="inlineStr">
         <is>
-          <t>2025.12 인증 → 2026.01 공식 출시</t>
+          <t>2025.11 인증 → 2026.01 공식 출시</t>
+        </is>
+      </c>
+      <c r="F9" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인증현황 No.31(2025.11.27) + 연혁 「2025.12 MDA 인증 획득」·「2026.01 말레이시아 공식 출시」</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="63" t="inlineStr">
         <is>
-          <t>말레이시아 UiTM</t>
+          <t>말레이시아</t>
         </is>
       </c>
       <c r="C10" s="53" t="inlineStr">
         <is>
-          <t>의과대학</t>
+          <t>의료기기청(MDA)</t>
         </is>
       </c>
       <c r="D10" s="53" t="inlineStr">
         <is>
-          <t>임상 협력</t>
+          <t>angel SUIT H10 (AS-H10-3BB 외 1건)</t>
         </is>
       </c>
       <c r="E10" s="53" t="inlineStr">
         <is>
-          <t>2022.05 전략적 협약(MOA)</t>
+          <t>2026.04 인증 획득</t>
+        </is>
+      </c>
+      <c r="F10" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인증현황 No.33(2026.04.28~2031.04.27) + 사업의 내용 「angel SUIT H10 말레이시아 인허가 완료」</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="63" t="inlineStr">
         <is>
-          <t>인도네시아·싱가포르</t>
+          <t>태국·베트남</t>
         </is>
       </c>
       <c r="C11" s="53" t="inlineStr">
         <is>
-          <t>각국 규제기관</t>
+          <t>TFDA / MOH</t>
         </is>
       </c>
       <c r="D11" s="53" t="inlineStr">
         <is>
-          <t>엔젤렉스 M20 외</t>
+          <t>angel SUIT H10</t>
         </is>
       </c>
       <c r="E11" s="53" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>진행 중 (현지 대리점 계약 체결)</t>
+        </is>
+      </c>
+      <c r="F11" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 사업의 내용 「태국 및 베트남 현지 파트너(대리점) 계약 체결, 제품 등록 및 인허가 진행 중」</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="63" t="inlineStr">
         <is>
-          <t>유럽</t>
+          <t>말레이시아 UiTM</t>
         </is>
       </c>
       <c r="C12" s="53" t="inlineStr">
         <is>
-          <t>CE MDR</t>
+          <t>(규제기관 아님 — 임상 협력)</t>
         </is>
       </c>
       <c r="D12" s="53" t="inlineStr">
         <is>
-          <t>엔젤렉스 M20 외</t>
+          <t>엔젤렉스 M20 2기 보급</t>
         </is>
       </c>
       <c r="E12" s="53" t="inlineStr">
         <is>
-          <t>지연 중</t>
+          <t>2022.05 전략적 협약(MOA)</t>
+        </is>
+      </c>
+      <c r="F12" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁 「2022.05 말레이시아 의과대학 UiTM과 전략적 협약(MOA) 체결」 + 연구개발활동(UiTM 병원 RCT 참여)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="63" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>인도네시아·싱가포르</t>
         </is>
       </c>
       <c r="C13" s="53" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>각국 규제기관</t>
         </is>
       </c>
       <c r="D13" s="53" t="inlineStr">
         <is>
-          <t>angel GEAR (ANGEL X)</t>
+          <t>엔젤렉스 M20 외</t>
         </is>
       </c>
       <c r="E13" s="53" t="inlineStr">
         <is>
-          <t>2022.12 등록 완료</t>
+          <t>확대 예정</t>
+        </is>
+      </c>
+      <c r="F13" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 사업의 내용 「인도네시아·싱가포르 등으로 인증 취득 범위를 확대해 나갈 예정」</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="63" t="inlineStr">
         <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="C14" s="53" t="inlineStr">
+        <is>
+          <t>CE MDR</t>
+        </is>
+      </c>
+      <c r="D14" s="53" t="inlineStr">
+        <is>
+          <t>엔젤렉스 M20 외</t>
+        </is>
+      </c>
+      <c r="E14" s="53" t="inlineStr">
+        <is>
+          <t>지연 중</t>
+        </is>
+      </c>
+      <c r="F14" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 「예측치 대비 실적 비교」 괴리사유 — 유럽 CE MDR 인증 지연</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="63" t="inlineStr">
+        <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="C14" s="53" t="inlineStr">
+      <c r="C15" s="53" t="inlineStr">
         <is>
           <t>FDA</t>
         </is>
       </c>
-      <c r="D14" s="53" t="inlineStr">
-        <is>
-          <t>의료기기 라인</t>
-        </is>
-      </c>
-      <c r="E14" s="53" t="inlineStr">
-        <is>
-          <t>단계적 추진</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>주) 말레이시아 의료기기 시장은 2027년까지 약 27억 달러 규모로 성장 전망 (리딩투자증권)</t>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>angel GEAR (ANGEL X)</t>
+        </is>
+      </c>
+      <c r="E15" s="53" t="inlineStr">
+        <is>
+          <t>2022.12 등록 완료</t>
+        </is>
+      </c>
+      <c r="F15" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁 「2022.12 'ANGEL X' 美 FDA 등록」</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="inlineStr">
+        <is>
+          <t>FDA</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="inlineStr">
+        <is>
+          <t>angel SUIT / 의료기기 라인</t>
+        </is>
+      </c>
+      <c r="E16" s="53" t="inlineStr">
+        <is>
+          <t>2026년 하반기 인증 준비 착수 예정</t>
+        </is>
+      </c>
+      <c r="F16" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 사업의 내용 「2026년 하반기부터 미국 FDA 인증 준비에 본격 착수할 예정」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>주1) '현황'의 시점은 인증서 발급일(인증현황 표) 기준. 연혁 표는 말레이시아 M20을 2025.12로 기재하여 발급일(2025.11.27)과 1개월 차이가 있음</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>기술 검증 이력</t>
+      <c r="A18" s="66" t="inlineStr">
+        <is>
+          <t>주2) 리딩투자증권(2025.12.16)은 태국·베트남 인허가를 '2023~2024년 획득'으로 서술하나, 공시(반기보고서)의 2025.06/2025.07과 불일치하므로 공시를 우선 적용</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>시기</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="63" t="inlineStr">
-        <is>
-          <t>2018.02</t>
-        </is>
-      </c>
-      <c r="C20" s="53" t="inlineStr">
-        <is>
-          <t>행사</t>
-        </is>
-      </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>워크온슈트 평창 패럴림픽 성화봉송 지원</t>
-        </is>
-      </c>
-      <c r="E20" s="53" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="63" t="inlineStr">
-        <is>
-          <t>2018.12</t>
-        </is>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
-        <is>
-          <t>수상</t>
-        </is>
-      </c>
-      <c r="D21" s="53" t="inlineStr">
-        <is>
-          <t>2018 올해의 대한민국 로봇기업</t>
-        </is>
-      </c>
-      <c r="E21" s="53" t="inlineStr"/>
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>주3) 말레이시아 의료기기 시장 2027년까지 약 27억 달러 전망 — 리딩투자증권(2025.12.16), 2차 자료</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="63" t="inlineStr">
-        <is>
-          <t>2020.11</t>
-        </is>
-      </c>
-      <c r="C22" s="53" t="inlineStr">
-        <is>
-          <t>수상</t>
-        </is>
-      </c>
-      <c r="D22" s="53" t="inlineStr">
-        <is>
-          <t>제2회 사이배슬론 전동형 외골격 금메달·동메달</t>
-        </is>
-      </c>
-      <c r="E22" s="53" t="inlineStr"/>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>해외 인증서 상세 (유효기간 포함)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="63" t="inlineStr">
-        <is>
-          <t>2022.10</t>
-        </is>
-      </c>
-      <c r="C23" s="53" t="inlineStr">
-        <is>
-          <t>선정</t>
-        </is>
-      </c>
-      <c r="D23" s="53" t="inlineStr">
-        <is>
-          <t>국가연구개발 우수성과 100선 (과학기술정보통신부)</t>
-        </is>
-      </c>
-      <c r="E23" s="53" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>인증 명칭</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>대상 모델</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>유효기간</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>출처 (행별)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>2023.02</t>
+          <t>태국</t>
         </is>
       </c>
       <c r="C24" s="53" t="inlineStr">
         <is>
-          <t>선정</t>
+          <t>Active non-implantable devices for rehabilitation (Class 2)</t>
         </is>
       </c>
       <c r="D24" s="53" t="inlineStr">
         <is>
-          <t>산업통상자원부 기계·장비·로봇 분야 R&amp;D 우수성과</t>
-        </is>
-      </c>
-      <c r="E24" s="53" t="inlineStr"/>
+          <t>ANGEL LEGS MEDICAL (M20-B-C3)</t>
+        </is>
+      </c>
+      <c r="E24" s="53" t="inlineStr">
+        <is>
+          <t>2025.06.26 ~ 2029.12.31</t>
+        </is>
+      </c>
+      <c r="F24" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인증현황 No.28</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="63" t="inlineStr">
         <is>
-          <t>2023.12</t>
+          <t>베트남</t>
         </is>
       </c>
       <c r="C25" s="53" t="inlineStr">
         <is>
-          <t>선정</t>
+          <t>Gait training and support robot System (Class B)</t>
         </is>
       </c>
       <c r="D25" s="53" t="inlineStr">
         <is>
-          <t>산업통상자원부 산업기술 대표 성과 10선 (워크온슈트)</t>
-        </is>
-      </c>
-      <c r="E25" s="53" t="inlineStr"/>
+          <t>ANGEL LEGS M20 (M20-B-C3 외 1건)</t>
+        </is>
+      </c>
+      <c r="E25" s="53" t="inlineStr">
+        <is>
+          <t>2025.07.07 ~ 2030.07.07</t>
+        </is>
+      </c>
+      <c r="F25" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인증현황 No.29</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>2024.06</t>
+          <t>말레이시아</t>
         </is>
       </c>
       <c r="C26" s="53" t="inlineStr">
         <is>
-          <t>수상</t>
+          <t>Wearable Walking Rehabilitation Robot (Class B)</t>
         </is>
       </c>
       <c r="D26" s="53" t="inlineStr">
         <is>
-          <t>angel GEAR 독일 레드닷 디자인 어워드</t>
-        </is>
-      </c>
-      <c r="E26" s="53" t="inlineStr"/>
+          <t>ANGEL LEGS M20 (M20-B-C3 외 1건)</t>
+        </is>
+      </c>
+      <c r="E26" s="53" t="inlineStr">
+        <is>
+          <t>2025.11.27 ~ 2030.11.26</t>
+        </is>
+      </c>
+      <c r="F26" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인증현황 No.31</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="63" t="inlineStr">
         <is>
+          <t>말레이시아</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>Powered lower extremity exoskeleton (Class B)</t>
+        </is>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>ANGEL SUIT H10 (AS-H10-3BB 외 1건)</t>
+        </is>
+      </c>
+      <c r="E27" s="53" t="inlineStr">
+        <is>
+          <t>2026.04.28 ~ 2031.04.27</t>
+        </is>
+      </c>
+      <c r="F27" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인증현황 No.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>기술 검증 이력</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>시기</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>출처 (행별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>2018.02</t>
+        </is>
+      </c>
+      <c r="C32" s="53" t="inlineStr">
+        <is>
+          <t>행사</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="inlineStr">
+        <is>
+          <t>워크온슈트 평창 패럴림픽 성화봉송 행사지원</t>
+        </is>
+      </c>
+      <c r="E32" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C33" s="53" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>올해의 대한민국 로봇기업</t>
+        </is>
+      </c>
+      <c r="E33" s="80" t="inlineStr">
+        <is>
+          <t>한국IR협의회(2024.09.26) 연혁 — 반기보고서 연혁에는 미기재 (2차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="63" t="inlineStr">
+        <is>
+          <t>2020.11</t>
+        </is>
+      </c>
+      <c r="C34" s="53" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="inlineStr">
+        <is>
+          <t>국제 사이보그 올림픽(Cybathlon) 전동형 외골격 금메달·동메달</t>
+        </is>
+      </c>
+      <c r="E34" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="63" t="inlineStr">
+        <is>
+          <t>2022.10</t>
+        </is>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>선정</t>
+        </is>
+      </c>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>국가연구개발 우수성과 100선 (기계소재 분야, 과학기술정보통신부)</t>
+        </is>
+      </c>
+      <c r="E35" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="63" t="inlineStr">
+        <is>
+          <t>2022.12</t>
+        </is>
+      </c>
+      <c r="C36" s="53" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="inlineStr">
+        <is>
+          <t>엔젤렉스 M20 의료기기 3등급 품목허가</t>
+        </is>
+      </c>
+      <c r="E36" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="63" t="inlineStr">
+        <is>
+          <t>2023.02</t>
+        </is>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>선정</t>
+        </is>
+      </c>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>산업통상자원부 기계·장비·로봇 분야 R&amp;D 우수성과</t>
+        </is>
+      </c>
+      <c r="E37" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="63" t="inlineStr">
+        <is>
+          <t>2023.12</t>
+        </is>
+      </c>
+      <c r="C38" s="53" t="inlineStr">
+        <is>
+          <t>선정</t>
+        </is>
+      </c>
+      <c r="D38" s="53" t="inlineStr">
+        <is>
+          <t>산업통상자원부 산업기술 대표 성과 10선 (워크온슈트)</t>
+        </is>
+      </c>
+      <c r="E38" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="63" t="inlineStr">
+        <is>
+          <t>2024.06</t>
+        </is>
+      </c>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="D39" s="53" t="inlineStr">
+        <is>
+          <t>angel GEAR 독일 2024 레드닷 디자인 어워드 디자인 부문</t>
+        </is>
+      </c>
+      <c r="E39" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="63" t="inlineStr">
+        <is>
           <t>2024.07</t>
         </is>
       </c>
-      <c r="C27" s="53" t="inlineStr">
+      <c r="C40" s="53" t="inlineStr">
         <is>
           <t>논문</t>
         </is>
       </c>
-      <c r="D27" s="53" t="inlineStr">
-        <is>
-          <t>JAMA Network Open 게재 (뇌성마비 아동 90명 임상)</t>
-        </is>
-      </c>
-      <c r="E27" s="53" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="63" t="inlineStr">
+      <c r="D40" s="53" t="inlineStr">
+        <is>
+          <t>JAMA Network Open 게재 — 뇌성마비 아동 90명 지상 보행 훈련</t>
+        </is>
+      </c>
+      <c r="E40" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁 + 사업의 내용(5개 의료기관, 2021.09~2023.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="63" t="inlineStr">
         <is>
           <t>2024.10</t>
         </is>
       </c>
-      <c r="C28" s="53" t="inlineStr">
+      <c r="C41" s="53" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="D28" s="53" t="inlineStr">
-        <is>
-          <t>제3회 사이배슬론 전동형 외골격 금메달 (2연패)</t>
-        </is>
-      </c>
-      <c r="E28" s="53" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="53" t="inlineStr">
+      <c r="D41" s="53" t="inlineStr">
+        <is>
+          <t>제3회 사이배슬론 전동형 외골격 금메달 (2회 연속)</t>
+        </is>
+      </c>
+      <c r="E41" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>2025 (게재)</t>
+        </is>
+      </c>
+      <c r="C42" s="53" t="inlineStr">
         <is>
           <t>논문</t>
         </is>
       </c>
-      <c r="D29" s="53" t="inlineStr">
-        <is>
-          <t>Stroke (IF 8.9) 게재 (급성기 뇌졸중 160명 다기관 RCT)</t>
-        </is>
-      </c>
-      <c r="E29" s="53" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="63" t="inlineStr">
+      <c r="D42" s="53" t="inlineStr">
+        <is>
+          <t>Stroke (IF 8.9) 게재 — 급성기 뇌졸중 160명 다기관 RCT</t>
+        </is>
+      </c>
+      <c r="E42" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연구개발활동 (삼성서울병원·말레이시아 UiTM 등 6개 기관, 2021.09~2023.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="63" t="inlineStr">
         <is>
           <t>2025.12</t>
         </is>
       </c>
-      <c r="C30" s="53" t="inlineStr">
+      <c r="C43" s="53" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="D30" s="53" t="inlineStr">
-        <is>
-          <t>범부처 의료기기 R&amp;D 어워즈 한국연구재단 이사장상</t>
-        </is>
-      </c>
-      <c r="E30" s="53" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="63" t="inlineStr">
+      <c r="D43" s="53" t="inlineStr">
+        <is>
+          <t>2025 범부처 의료기기 R&amp;D 어워즈 한국연구재단 이사장상</t>
+        </is>
+      </c>
+      <c r="E43" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁 (본문에는 '전문기관장 표창'으로 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t>2026.03</t>
         </is>
       </c>
-      <c r="C31" s="53" t="inlineStr">
+      <c r="C44" s="53" t="inlineStr">
         <is>
           <t>선정</t>
         </is>
       </c>
-      <c r="D31" s="53" t="inlineStr">
-        <is>
-          <t>파이낸셜타임즈 아시아태평양 고성장 기업 500</t>
-        </is>
-      </c>
-      <c r="E31" s="53" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="43" t="inlineStr">
+      <c r="D44" s="53" t="inlineStr">
+        <is>
+          <t>파이낸셜타임즈 아시아태평양지역 고성장 기업 500</t>
+        </is>
+      </c>
+      <c r="E44" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+      <c r="C45" s="53" t="inlineStr">
+        <is>
+          <t>국가과제</t>
+        </is>
+      </c>
+      <c r="D45" s="53" t="inlineStr">
+        <is>
+          <t>범부처 '브레인 투 로봇' 개발 과제 주관기관 선정</t>
+        </is>
+      </c>
+      <c r="E45" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>지식재산권</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>수치</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>출처 (행별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="63" t="inlineStr">
         <is>
           <t>특허 출원</t>
         </is>
       </c>
-      <c r="C33" s="64" t="n">
+      <c r="C50" s="53" t="n">
         <v>75</v>
       </c>
-      <c r="D33" s="65" t="inlineStr">
+      <c r="D50" s="53" t="inlineStr">
         <is>
           <t>건</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="43" t="inlineStr">
+      <c r="E50" s="80" t="inlineStr">
+        <is>
+          <t>한국IR협의회 기업리서치센터(2024.09.26) — 2024년 기준 (2차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="63" t="inlineStr">
         <is>
           <t>임상 케이스 논문</t>
         </is>
       </c>
-      <c r="C34" s="64" t="n">
+      <c r="C51" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="65" t="inlineStr">
+      <c r="D51" s="53" t="inlineStr">
         <is>
           <t>편</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>핵심특허: 보행 의도 파악(10-1317354) / 정밀 힘 제어(10-1477401) / 보행 주기별 제어(10-2162485)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>출처: 한국IR협의회 기업리서치센터(2024.09.26), 제10기 반기보고서</t>
+      <c r="E51" s="80" t="inlineStr">
+        <is>
+          <t>한국IR협의회 기업리서치센터(2024.09.26) (2차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>핵심특허: 보행 의도 파악(10-1317354) / 정밀 힘 제어(10-1477401) / 보행 주기별 제어(10-2162485) — 한국IR협의회(2024.09.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>■ 출처 표기 원칙: '반기보고서 ○○'은 제10기 반기보고서(2026.06.30 기준) 1차 공시자료, 그 외 (2차)는 증권사·기관 리포트로 IM 인용 시 원문 재확인 필요</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -3384,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A2:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3396,7 +3781,6 @@
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
@@ -3411,7 +3795,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -3531,8 +3914,6 @@
       </c>
       <c r="G9" s="53" t="inlineStr"/>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="16" t="inlineStr">
         <is>
@@ -3634,8 +4015,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="16" t="inlineStr">
         <is>
@@ -3650,7 +4029,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="C22" s="72" t="inlineStr">
         <is>
@@ -3829,8 +4207,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="B32" s="76" t="inlineStr">
         <is>
@@ -3851,7 +4227,6 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
@@ -6205,7 +6580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A2:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6220,7 +6595,6 @@
     <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
@@ -6235,7 +6609,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -6667,7 +7040,6 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>

--- a/out/엔젤로보틱스_리서치자료.xlsx
+++ b/out/엔젤로보틱스_리서치자료.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -152,6 +152,12 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -186,7 +192,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -246,11 +252,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -430,6 +437,30 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2337,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G55"/>
+  <dimension ref="A2:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2851,13 +2882,20 @@
       <c r="F33" s="53" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="16" t="inlineStr">
+      <c r="A36" s="81" t="n"/>
+      <c r="B36" s="82" t="inlineStr">
         <is>
           <t>수가 체계 및 산업 구조</t>
         </is>
       </c>
+      <c r="C36" s="81" t="n"/>
+      <c r="D36" s="81" t="n"/>
+      <c r="E36" s="81" t="n"/>
+      <c r="F36" s="81" t="n"/>
+      <c r="G36" s="81" t="n"/>
     </row>
     <row r="37">
+      <c r="A37" s="81" t="n"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
           <t>구분</t>
@@ -2868,292 +2906,604 @@
           <t>내용</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr"/>
+      <c r="D37" s="83" t="n"/>
+      <c r="E37" s="83" t="n"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>출처 (행별)</t>
+        </is>
+      </c>
+      <c r="G37" s="83" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="63" t="inlineStr">
+      <c r="A38" s="81" t="n"/>
+      <c r="B38" s="84" t="inlineStr">
         <is>
           <t>급여화 시점</t>
         </is>
       </c>
-      <c r="C38" s="53" t="inlineStr">
-        <is>
-          <t>2022년 2월 보행재활로봇 건강보험 급여화 적용</t>
-        </is>
-      </c>
-      <c r="D38" s="53" t="inlineStr"/>
-      <c r="E38" s="53" t="inlineStr"/>
+      <c r="C38" s="85" t="inlineStr">
+        <is>
+          <t>2022.02.01 적용 — 보건복지부 고시 제2022-4호로 「선별급여 지정 및 실시 등에 관한 기준」 개정·발령 (분류번호 사130나 주2)</t>
+        </is>
+      </c>
+      <c r="D38" s="86" t="n"/>
+      <c r="E38" s="86" t="n"/>
+      <c r="F38" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 「수가 코드 적용이 필수적인 시장」 + 인용된 고시 제2022-4호 표</t>
+        </is>
+      </c>
+      <c r="G38" s="86" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="63" t="inlineStr">
-        <is>
-          <t>적용 대상</t>
-        </is>
-      </c>
-      <c r="C39" s="53" t="inlineStr">
-        <is>
-          <t>발병 6개월 이내 뇌졸중 환자 (FAC 2등급 이하), 로봇정형운동장치 3등급 보행로봇에 한함</t>
-        </is>
-      </c>
-      <c r="D39" s="53" t="inlineStr"/>
-      <c r="E39" s="53" t="inlineStr"/>
+      <c r="A39" s="81" t="n"/>
+      <c r="B39" s="84" t="inlineStr">
+        <is>
+          <t>급여 형태</t>
+        </is>
+      </c>
+      <c r="C39" s="85" t="inlineStr">
+        <is>
+          <t>선별급여 / 본인부담률 50% / 평가주기 5년</t>
+        </is>
+      </c>
+      <c r="D39" s="86" t="n"/>
+      <c r="E39" s="86" t="n"/>
+      <c r="F39" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인용 고시 제2022-4호 표</t>
+        </is>
+      </c>
+      <c r="G39" s="86" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="63" t="inlineStr">
+      <c r="A40" s="81" t="n"/>
+      <c r="B40" s="84" t="inlineStr">
+        <is>
+          <t>적용 대상 (공시 확인)</t>
+        </is>
+      </c>
+      <c r="C40" s="85" t="inlineStr">
+        <is>
+          <t>MM304: 뇌졸중 환자에게 로봇을 사용하여 보행훈련 30분 이상 실시한 경우  |  MM302(모수 행위): 편마비·하지마비·사지마비·뇌성마비 등 중추신경계 질환자 및 사지절단자 등 보행 동작 제한자</t>
+        </is>
+      </c>
+      <c r="D40" s="86" t="n"/>
+      <c r="E40" s="86" t="n"/>
+      <c r="F40" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인용 건강보험 행위 급여목록 사-130 (주1·주2)</t>
+        </is>
+      </c>
+      <c r="G40" s="86" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="81" t="n"/>
+      <c r="B41" s="87" t="inlineStr">
+        <is>
+          <t>⚠ 적용 대상 (미확인)</t>
+        </is>
+      </c>
+      <c r="C41" s="85" t="inlineStr">
+        <is>
+          <t>'발병 6개월 이내', 'FAC 2등급 이하' 등 세부 급여기준 — 업로드된 공시·리포트 어디에도 근거 없음</t>
+        </is>
+      </c>
+      <c r="D41" s="86" t="n"/>
+      <c r="E41" s="86" t="n"/>
+      <c r="F41" s="80" t="inlineStr">
+        <is>
+          <t>웹 리서치 기반. 심평원 고시 원문 대조 전까지 IM 인용 불가</t>
+        </is>
+      </c>
+      <c r="G41" s="86" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="81" t="n"/>
+      <c r="B42" s="84" t="inlineStr">
+        <is>
+          <t>수가 점수</t>
+        </is>
+      </c>
+      <c r="C42" s="85" t="inlineStr">
+        <is>
+          <t>MM302 177.42점 / MM304 317.87점 별도 산정</t>
+        </is>
+      </c>
+      <c r="D42" s="86" t="n"/>
+      <c r="E42" s="86" t="n"/>
+      <c r="F42" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인용 건강보험 행위 급여목록 사-130</t>
+        </is>
+      </c>
+      <c r="G42" s="86" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="81" t="n"/>
+      <c r="B43" s="84" t="inlineStr">
         <is>
           <t>수가 코드</t>
         </is>
       </c>
-      <c r="C40" s="53" t="inlineStr">
-        <is>
-          <t>로봇보행재활(MM304) / 보행치료(MM302) / 동작분석(EZ774)</t>
-        </is>
-      </c>
-      <c r="D40" s="53" t="inlineStr"/>
-      <c r="E40" s="53" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="63" t="inlineStr">
-        <is>
-          <t>산업 특성</t>
-        </is>
-      </c>
-      <c r="C41" s="53" t="inlineStr">
-        <is>
-          <t>국산 재활로봇 다수가 신의료기술평가에서 '기존기술' 판정을 받아 별도 수가 미확보. 급여 미적용 시 환자 전액 부담으로 고가 장비 판매가 사실상 곤란</t>
-        </is>
-      </c>
-      <c r="D41" s="53" t="inlineStr"/>
-      <c r="E41" s="53" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="63" t="inlineStr">
+      <c r="C43" s="85" t="inlineStr">
+        <is>
+          <t>MM304 로봇보행재활 (2022.12 적용 개시, 웨어러블 로봇 최초) / MM302 보행치료 / EZ774 동작분석</t>
+        </is>
+      </c>
+      <c r="D43" s="86" t="n"/>
+      <c r="E43" s="86" t="n"/>
+      <c r="F43" s="80" t="inlineStr">
+        <is>
+          <t>MM302·MM304는 반기보고서. EZ774는 한국IR협의회(2024.09.26) 도표에만 등장 (2차)</t>
+        </is>
+      </c>
+      <c r="G43" s="86" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="81" t="n"/>
+      <c r="B44" s="84" t="inlineStr">
+        <is>
+          <t>시장 확대 근거</t>
+        </is>
+      </c>
+      <c r="C44" s="85" t="inlineStr">
+        <is>
+          <t>MM302 보행치료 수가 청구 건수·환자수 매년 증가, 2022년 신설 MM304 치료 시장도 큰 성장세</t>
+        </is>
+      </c>
+      <c r="D44" s="86" t="n"/>
+      <c r="E44" s="86" t="n"/>
+      <c r="F44" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 「사업의 내용」 (국민건강보험공단 자료 인용, 원자료 미첨부)</t>
+        </is>
+      </c>
+      <c r="G44" s="86" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="81" t="n"/>
+      <c r="B45" s="87" t="inlineStr">
+        <is>
+          <t>⚠ 산업 특성</t>
+        </is>
+      </c>
+      <c r="C45" s="85" t="inlineStr">
+        <is>
+          <t>국산 재활로봇 다수가 신의료기술평가에서 '기존기술' 판정을 받아 별도 수가 미확보 → 환자 전액 부담으로 고가 장비 판매 곤란</t>
+        </is>
+      </c>
+      <c r="D45" s="86" t="n"/>
+      <c r="E45" s="86" t="n"/>
+      <c r="F45" s="80" t="inlineStr">
+        <is>
+          <t>웹 리서치 기반. 공시·증권사 리포트에 근거 없음 — 원문 확인 필요</t>
+        </is>
+      </c>
+      <c r="G45" s="86" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="81" t="n"/>
+      <c r="B46" s="84" t="inlineStr">
         <is>
           <t>정책 방향</t>
         </is>
       </c>
-      <c r="C42" s="53" t="inlineStr">
-        <is>
-          <t>보건복지부, 척수손상·파킨슨 등으로 수가 적응증 확대 추진</t>
-        </is>
-      </c>
-      <c r="D42" s="53" t="inlineStr"/>
-      <c r="E42" s="53" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="63" t="inlineStr">
+      <c r="C46" s="85" t="inlineStr">
+        <is>
+          <t>뇌졸중 외 척수손상·파킨슨 등 기타 질환에 대한 치료효과성 입증 시 수가화 추진 (보건복지부)</t>
+        </is>
+      </c>
+      <c r="D46" s="86" t="n"/>
+      <c r="E46" s="86" t="n"/>
+      <c r="F46" s="80" t="inlineStr">
+        <is>
+          <t>한국IR협의회 기업리서치센터(2024.09.26) (2차)</t>
+        </is>
+      </c>
+      <c r="G46" s="86" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="81" t="n"/>
+      <c r="B47" s="84" t="inlineStr">
         <is>
           <t>상반된 흐름</t>
         </is>
       </c>
-      <c r="C43" s="53" t="inlineStr">
-        <is>
-          <t>산업안전 분야는 '스마트 안전장비 보급확산' 예산 감소로 B2G 시장 축소</t>
-        </is>
-      </c>
-      <c r="D43" s="53" t="inlineStr"/>
-      <c r="E43" s="53" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="16" t="inlineStr">
+      <c r="C47" s="85" t="inlineStr">
+        <is>
+          <t>'스마트 안전장비 보급확산' 등 정부주도 보급사업의 보조금 감소로 angel GEAR B2G 시장 축소</t>
+        </is>
+      </c>
+      <c r="D47" s="86" t="n"/>
+      <c r="E47" s="86" t="n"/>
+      <c r="F47" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 「예측치 대비 실적 비교」 괴리사유 (2025년·2026년 반기 모두 기재)</t>
+        </is>
+      </c>
+      <c r="G47" s="86" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="88" t="inlineStr">
+        <is>
+          <t>주) 엔젤렉스 M20은 2022.12.14 웨어러블 로봇 최초로 의료기기 3등급(로봇보조정형용운동장치) 품목허가를 받아 MM304 적용이 가능해짐 — 반기보고서 연혁·사업의 내용</t>
+        </is>
+      </c>
+      <c r="B48" s="89" t="n"/>
+      <c r="C48" s="90" t="n"/>
+      <c r="D48" s="90" t="n"/>
+      <c r="E48" s="90" t="n"/>
+      <c r="F48" s="90" t="n"/>
+      <c r="G48" s="81" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t>■ ⚠ 표시 2개 행은 웹 리서치 기반으로 1차 근거가 없음. 외부 배포용 IM 인용 전 반드시 심평원·복지부 고시 원문으로 대조할 것</t>
+        </is>
+      </c>
+      <c r="B49" s="89" t="n"/>
+      <c r="C49" s="90" t="n"/>
+      <c r="D49" s="90" t="n"/>
+      <c r="E49" s="90" t="n"/>
+      <c r="F49" s="90" t="n"/>
+      <c r="G49" s="81" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="81" t="n"/>
+      <c r="B50" s="89" t="n"/>
+      <c r="C50" s="90" t="n"/>
+      <c r="D50" s="90" t="n"/>
+      <c r="E50" s="90" t="n"/>
+      <c r="F50" s="90" t="n"/>
+      <c r="G50" s="81" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="81" t="n"/>
+      <c r="B51" s="89" t="n"/>
+      <c r="C51" s="90" t="n"/>
+      <c r="D51" s="90" t="n"/>
+      <c r="E51" s="90" t="n"/>
+      <c r="F51" s="90" t="n"/>
+      <c r="G51" s="81" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="81" t="n"/>
+      <c r="B52" s="92" t="inlineStr">
         <is>
           <t>국내외 경쟁사</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="6" t="inlineStr">
+      <c r="C52" s="90" t="n"/>
+      <c r="D52" s="90" t="n"/>
+      <c r="E52" s="90" t="n"/>
+      <c r="F52" s="90" t="n"/>
+      <c r="G52" s="81" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="81" t="n"/>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>설립/상장</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="63" t="inlineStr">
+      <c r="F53" s="83" t="n"/>
+      <c r="G53" s="83" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="81" t="n"/>
+      <c r="B54" s="84" t="inlineStr">
         <is>
           <t>국내 상장</t>
         </is>
       </c>
-      <c r="C48" s="53" t="inlineStr">
+      <c r="C54" s="85" t="inlineStr">
         <is>
           <t>피앤에스로보틱스 (460940)</t>
         </is>
       </c>
-      <c r="D48" s="53" t="inlineStr">
+      <c r="D54" s="85" t="inlineStr">
         <is>
           <t>2003년 설립 / 2024.07 상장</t>
         </is>
       </c>
-      <c r="E48" s="53" t="inlineStr">
-        <is>
-          <t>보행재활훈련 로봇 Walkbot (트레드밀 기반 고정형)</t>
-        </is>
-      </c>
-      <c r="F48" s="53" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="63" t="inlineStr">
+      <c r="E54" s="85" t="inlineStr">
+        <is>
+          <t>보행재활훈련 로봇 Walkbot — 트레드밀 기반 고정형, 해외매출 비중 높음 (동사와 제품 형태·시장 상이)</t>
+        </is>
+      </c>
+      <c r="F54" s="86" t="n"/>
+      <c r="G54" s="86" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="88" t="n"/>
+      <c r="B55" s="84" t="inlineStr">
         <is>
           <t>국내 비상장</t>
         </is>
       </c>
-      <c r="C49" s="53" t="inlineStr">
+      <c r="C55" s="85" t="inlineStr">
         <is>
           <t>FRT로보틱스</t>
         </is>
       </c>
-      <c r="D49" s="53" t="inlineStr">
+      <c r="D55" s="85" t="inlineStr">
         <is>
           <t>2015년</t>
         </is>
       </c>
-      <c r="E49" s="53" t="inlineStr">
+      <c r="E55" s="85" t="inlineStr">
         <is>
           <t>웨어러블 로봇</t>
         </is>
       </c>
-      <c r="F49" s="53" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="63" t="inlineStr">
+      <c r="F55" s="86" t="n"/>
+      <c r="G55" s="86" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="81" t="n"/>
+      <c r="B56" s="84" t="inlineStr">
         <is>
           <t>국내 비상장</t>
         </is>
       </c>
-      <c r="C50" s="53" t="inlineStr">
+      <c r="C56" s="85" t="inlineStr">
         <is>
           <t>헥사휴먼케어</t>
         </is>
       </c>
-      <c r="D50" s="53" t="inlineStr">
+      <c r="D56" s="85" t="inlineStr">
         <is>
           <t>2016년</t>
         </is>
       </c>
-      <c r="E50" s="53" t="inlineStr">
+      <c r="E56" s="85" t="inlineStr">
         <is>
           <t>웨어러블 로봇</t>
         </is>
       </c>
-      <c r="F50" s="53" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="63" t="inlineStr">
+      <c r="F56" s="86" t="n"/>
+      <c r="G56" s="86" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="81" t="n"/>
+      <c r="B57" s="84" t="inlineStr">
         <is>
           <t>국내 비상장</t>
         </is>
       </c>
-      <c r="C51" s="53" t="inlineStr">
+      <c r="C57" s="85" t="inlineStr">
         <is>
           <t>코스모로보틱스</t>
         </is>
       </c>
-      <c r="D51" s="53" t="inlineStr">
+      <c r="D57" s="85" t="inlineStr">
         <is>
           <t>2016년</t>
         </is>
       </c>
-      <c r="E51" s="53" t="inlineStr">
+      <c r="E57" s="85" t="inlineStr">
         <is>
           <t>웨어러블 로봇</t>
         </is>
       </c>
-      <c r="F51" s="53" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="63" t="inlineStr">
+      <c r="F57" s="86" t="n"/>
+      <c r="G57" s="86" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="81" t="n"/>
+      <c r="B58" s="84" t="inlineStr">
         <is>
           <t>해외 상장</t>
         </is>
       </c>
-      <c r="C52" s="53" t="inlineStr">
+      <c r="C58" s="85" t="inlineStr">
         <is>
           <t>라이프워드 (구 리워크, 나스닥)</t>
         </is>
       </c>
-      <c r="D52" s="53" t="inlineStr">
+      <c r="D58" s="85" t="inlineStr">
         <is>
           <t>이스라엘</t>
         </is>
       </c>
-      <c r="E52" s="53" t="inlineStr">
+      <c r="E58" s="85" t="inlineStr">
         <is>
           <t>2014.06 FDA 하지 외골격로봇 허가</t>
         </is>
       </c>
-      <c r="F52" s="53" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="63" t="inlineStr">
+      <c r="F58" s="86" t="n"/>
+      <c r="G58" s="86" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="81" t="n"/>
+      <c r="B59" s="84" t="inlineStr">
         <is>
           <t>해외 상장</t>
         </is>
       </c>
-      <c r="C53" s="53" t="inlineStr">
+      <c r="C59" s="85" t="inlineStr">
         <is>
           <t>Ekso Bionics (나스닥)</t>
         </is>
       </c>
-      <c r="D53" s="53" t="inlineStr">
+      <c r="D59" s="85" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="E53" s="53" t="inlineStr">
+      <c r="E59" s="85" t="inlineStr">
         <is>
           <t>Ekso GT 척수손상·뇌졸중 FDA 허가</t>
         </is>
       </c>
-      <c r="F53" s="53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="63" t="inlineStr">
+      <c r="F59" s="86" t="n"/>
+      <c r="G59" s="86" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="81" t="n"/>
+      <c r="B60" s="84" t="inlineStr">
         <is>
           <t>해외</t>
         </is>
       </c>
-      <c r="C54" s="53" t="inlineStr">
+      <c r="C60" s="85" t="inlineStr">
         <is>
           <t>사이버다인</t>
         </is>
       </c>
-      <c r="D54" s="53" t="inlineStr">
+      <c r="D60" s="85" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="E54" s="53" t="inlineStr">
-        <is>
-          <t>HAL 시리즈</t>
-        </is>
-      </c>
-      <c r="F54" s="53" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="30" t="inlineStr">
-        <is>
-          <t>참고) 세브란스 재활병원은 7개 재활로봇을 보유하고 보행재활을 5단계로 운영하며, 엔젤렉스는 회복이 가장 진행된 5단계에 배치</t>
-        </is>
-      </c>
+      <c r="E60" s="85" t="inlineStr">
+        <is>
+          <t>HAL 시리즈 — 생체신호(근전도) 센서 사용, 탈의 후 피부 부착 방식</t>
+        </is>
+      </c>
+      <c r="F60" s="86" t="n"/>
+      <c r="G60" s="86" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="88" t="inlineStr">
+        <is>
+          <t>출처: 반기보고서 「경쟁 현황 및 비교우위 사항」, 한국IR협의회(2024.09.26), 리딩투자증권(2025.12.16)</t>
+        </is>
+      </c>
+      <c r="B61" s="81" t="n"/>
+      <c r="C61" s="81" t="n"/>
+      <c r="D61" s="81" t="n"/>
+      <c r="E61" s="81" t="n"/>
+      <c r="F61" s="81" t="n"/>
+      <c r="G61" s="81" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="88" t="inlineStr">
+        <is>
+          <t>참고) 세브란스 재활병원은 7개 재활로봇을 보유하고 보행재활을 5단계로 운영하며, 엔젤렉스는 회복이 가장 진행된 5단계에 배치 — 한국IR협의회</t>
+        </is>
+      </c>
+      <c r="B62" s="81" t="n"/>
+      <c r="C62" s="81" t="n"/>
+      <c r="D62" s="81" t="n"/>
+      <c r="E62" s="81" t="n"/>
+      <c r="F62" s="81" t="n"/>
+      <c r="G62" s="81" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="81" t="n"/>
+      <c r="B63" s="81" t="n"/>
+      <c r="C63" s="81" t="n"/>
+      <c r="D63" s="81" t="n"/>
+      <c r="E63" s="81" t="n"/>
+      <c r="F63" s="81" t="n"/>
+      <c r="G63" s="81" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="81" t="n"/>
+      <c r="B64" s="81" t="n"/>
+      <c r="C64" s="81" t="n"/>
+      <c r="D64" s="81" t="n"/>
+      <c r="E64" s="81" t="n"/>
+      <c r="F64" s="81" t="n"/>
+      <c r="G64" s="81" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="81" t="n"/>
+      <c r="B65" s="81" t="n"/>
+      <c r="C65" s="81" t="n"/>
+      <c r="D65" s="81" t="n"/>
+      <c r="E65" s="81" t="n"/>
+      <c r="F65" s="81" t="n"/>
+      <c r="G65" s="81" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="81" t="n"/>
+      <c r="B66" s="81" t="n"/>
+      <c r="C66" s="81" t="n"/>
+      <c r="D66" s="81" t="n"/>
+      <c r="E66" s="81" t="n"/>
+      <c r="F66" s="81" t="n"/>
+      <c r="G66" s="81" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="81" t="n"/>
+      <c r="B67" s="81" t="n"/>
+      <c r="C67" s="81" t="n"/>
+      <c r="D67" s="81" t="n"/>
+      <c r="E67" s="81" t="n"/>
+      <c r="F67" s="81" t="n"/>
+      <c r="G67" s="81" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="81" t="n"/>
+      <c r="B68" s="81" t="n"/>
+      <c r="C68" s="81" t="n"/>
+      <c r="D68" s="81" t="n"/>
+      <c r="E68" s="81" t="n"/>
+      <c r="F68" s="81" t="n"/>
+      <c r="G68" s="81" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="81" t="n"/>
+      <c r="B69" s="81" t="n"/>
+      <c r="C69" s="81" t="n"/>
+      <c r="D69" s="81" t="n"/>
+      <c r="E69" s="81" t="n"/>
+      <c r="F69" s="81" t="n"/>
+      <c r="G69" s="81" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C47:E47"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/out/엔젤로보틱스_리서치자료.xlsx
+++ b/out/엔젤로보틱스_리서치자료.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -158,6 +158,22 @@
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F6F3D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F6F3D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F6F3D"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -192,7 +208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -253,11 +269,22 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,6 +488,34 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1612,14 +1667,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="63" t="inlineStr">
-        <is>
-          <t>태국·베트남</t>
+      <c r="B11" s="93" t="inlineStr">
+        <is>
+          <t>베트남</t>
         </is>
       </c>
       <c r="C11" s="53" t="inlineStr">
         <is>
-          <t>TFDA / MOH</t>
+          <t>보건복지부(MOH)</t>
         </is>
       </c>
       <c r="D11" s="53" t="inlineStr">
@@ -1629,12 +1684,12 @@
       </c>
       <c r="E11" s="53" t="inlineStr">
         <is>
-          <t>진행 중 (현지 대리점 계약 체결)</t>
+          <t>2026.08 Class B 의료기기 등록 완료</t>
         </is>
       </c>
       <c r="F11" s="80" t="inlineStr">
         <is>
-          <t>반기보고서 사업의 내용 「태국 및 베트남 현지 파트너(대리점) 계약 체결, 제품 등록 및 인허가 진행 중」</t>
+          <t>언론 보도(2026.08.05, ZDNet·로봇신문·더벨) — 반기보고서 기준일 이후 사건. 태국은 대리점 계약 후 등록 진행 중(반기보고서 사업의 내용)</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G69"/>
+  <dimension ref="A2:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2885,7 +2940,7 @@
       <c r="A36" s="81" t="n"/>
       <c r="B36" s="82" t="inlineStr">
         <is>
-          <t>수가 체계 및 산업 구조</t>
+          <t>수가 체계 ① 급여 제도 연혁</t>
         </is>
       </c>
       <c r="C36" s="81" t="n"/>
@@ -2898,7 +2953,7 @@
       <c r="A37" s="81" t="n"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>시점</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2919,19 +2974,19 @@
       <c r="A38" s="81" t="n"/>
       <c r="B38" s="84" t="inlineStr">
         <is>
-          <t>급여화 시점</t>
+          <t>2022.02.01</t>
         </is>
       </c>
       <c r="C38" s="85" t="inlineStr">
         <is>
-          <t>2022.02.01 적용 — 보건복지부 고시 제2022-4호로 「선별급여 지정 및 실시 등에 관한 기준」 개정·발령 (분류번호 사130나 주2)</t>
+          <t>선별급여 신설 — 고시 제2022-26호(행위). 항목명 「보행치료-뇌졸중 환자에서 로봇을 사용한 보행훈련」, 분류번호 사130나 주2, 본인부담률 50%, 평가주기 5년</t>
         </is>
       </c>
       <c r="D38" s="86" t="n"/>
       <c r="E38" s="86" t="n"/>
       <c r="F38" s="80" t="inlineStr">
         <is>
-          <t>반기보고서 「수가 코드 적용이 필수적인 시장」 + 인용된 고시 제2022-4호 표</t>
+          <t>반기보고서 인용 고시 제2022-4호 표 + 심평원 심사기준(시행 2022.02.01)</t>
         </is>
       </c>
       <c r="G38" s="86" t="n"/>
@@ -2940,228 +2995,257 @@
       <c r="A39" s="81" t="n"/>
       <c r="B39" s="84" t="inlineStr">
         <is>
-          <t>급여 형태</t>
+          <t>2022.12.14</t>
         </is>
       </c>
       <c r="C39" s="85" t="inlineStr">
         <is>
-          <t>선별급여 / 본인부담률 50% / 평가주기 5년</t>
+          <t>엔젤렉스 M20, 웨어러블 로봇 최초 의료기기 3등급(로봇보조정형용운동장치) 품목허가 → MM304 실제 적용 개시</t>
         </is>
       </c>
       <c r="D39" s="86" t="n"/>
       <c r="E39" s="86" t="n"/>
       <c r="F39" s="80" t="inlineStr">
         <is>
-          <t>반기보고서 인용 고시 제2022-4호 표</t>
+          <t>반기보고서 연혁·사업의 내용</t>
         </is>
       </c>
       <c r="G39" s="86" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="81" t="n"/>
-      <c r="B40" s="84" t="inlineStr">
-        <is>
-          <t>적용 대상 (공시 확인)</t>
+      <c r="B40" s="94" t="inlineStr">
+        <is>
+          <t>2026.07.30 고시
+2026.07.31 시행</t>
         </is>
       </c>
       <c r="C40" s="85" t="inlineStr">
         <is>
-          <t>MM304: 뇌졸중 환자에게 로봇을 사용하여 보행훈련 30분 이상 실시한 경우  |  MM302(모수 행위): 편마비·하지마비·사지마비·뇌성마비 등 중추신경계 질환자 및 사지절단자 등 보행 동작 제한자</t>
+          <t>급여대상 확대 — 보건복지부 고시 제2026-166호, 「요양급여의 적용기준 및 방법에 관한 세부사항」 일부개정. 2022년 2월 항목 신설 이래 최초의 대상 확대</t>
         </is>
       </c>
       <c r="D40" s="86" t="n"/>
       <c r="E40" s="86" t="n"/>
       <c r="F40" s="80" t="inlineStr">
         <is>
-          <t>반기보고서 인용 건강보험 행위 급여목록 사-130 (주1·주2)</t>
+          <t>보건복지부 고시 제2026-166호 (의약일보·병원신문·ZDNet 등 다수 보도) — 반기보고서 기준일(2026.06.30) 이후 사건으로 공시 미반영</t>
         </is>
       </c>
       <c r="G40" s="86" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="81" t="n"/>
-      <c r="B41" s="87" t="inlineStr">
-        <is>
-          <t>⚠ 적용 대상 (미확인)</t>
-        </is>
-      </c>
-      <c r="C41" s="85" t="inlineStr">
-        <is>
-          <t>'발병 6개월 이내', 'FAC 2등급 이하' 등 세부 급여기준 — 업로드된 공시·리포트 어디에도 근거 없음</t>
-        </is>
-      </c>
-      <c r="D41" s="86" t="n"/>
-      <c r="E41" s="86" t="n"/>
-      <c r="F41" s="80" t="inlineStr">
-        <is>
-          <t>웹 리서치 기반. 심평원 고시 원문 대조 전까지 IM 인용 불가</t>
-        </is>
-      </c>
-      <c r="G41" s="86" t="n"/>
+      <c r="B41" s="95" t="n"/>
+      <c r="C41" s="96" t="n"/>
+      <c r="D41" s="81" t="n"/>
+      <c r="E41" s="81" t="n"/>
+      <c r="F41" s="97" t="n"/>
+      <c r="G41" s="81" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="81" t="n"/>
-      <c r="B42" s="84" t="inlineStr">
-        <is>
-          <t>수가 점수</t>
-        </is>
-      </c>
-      <c r="C42" s="85" t="inlineStr">
-        <is>
-          <t>MM302 177.42점 / MM304 317.87점 별도 산정</t>
-        </is>
-      </c>
-      <c r="D42" s="86" t="n"/>
-      <c r="E42" s="86" t="n"/>
-      <c r="F42" s="80" t="inlineStr">
-        <is>
-          <t>반기보고서 인용 건강보험 행위 급여목록 사-130</t>
-        </is>
-      </c>
-      <c r="G42" s="86" t="n"/>
+      <c r="B42" s="98" t="n"/>
+      <c r="C42" s="96" t="n"/>
+      <c r="D42" s="81" t="n"/>
+      <c r="E42" s="81" t="n"/>
+      <c r="F42" s="97" t="n"/>
+      <c r="G42" s="81" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="81" t="n"/>
-      <c r="B43" s="84" t="inlineStr">
-        <is>
-          <t>수가 코드</t>
-        </is>
-      </c>
-      <c r="C43" s="85" t="inlineStr">
-        <is>
-          <t>MM304 로봇보행재활 (2022.12 적용 개시, 웨어러블 로봇 최초) / MM302 보행치료 / EZ774 동작분석</t>
-        </is>
-      </c>
-      <c r="D43" s="86" t="n"/>
-      <c r="E43" s="86" t="n"/>
-      <c r="F43" s="80" t="inlineStr">
-        <is>
-          <t>MM302·MM304는 반기보고서. EZ774는 한국IR협의회(2024.09.26) 도표에만 등장 (2차)</t>
-        </is>
-      </c>
-      <c r="G43" s="86" t="n"/>
+      <c r="B43" s="99" t="inlineStr">
+        <is>
+          <t>수가 체계 ② 급여기준 신구 대비 (2026.07.31 개정)</t>
+        </is>
+      </c>
+      <c r="C43" s="96" t="n"/>
+      <c r="D43" s="81" t="n"/>
+      <c r="E43" s="81" t="n"/>
+      <c r="F43" s="97" t="n"/>
+      <c r="G43" s="81" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="81" t="n"/>
-      <c r="B44" s="84" t="inlineStr">
-        <is>
-          <t>시장 확대 근거</t>
-        </is>
-      </c>
-      <c r="C44" s="85" t="inlineStr">
-        <is>
-          <t>MM302 보행치료 수가 청구 건수·환자수 매년 증가, 2022년 신설 MM304 치료 시장도 큰 성장세</t>
-        </is>
-      </c>
-      <c r="D44" s="86" t="n"/>
-      <c r="E44" s="86" t="n"/>
-      <c r="F44" s="80" t="inlineStr">
-        <is>
-          <t>반기보고서 「사업의 내용」 (국민건강보험공단 자료 인용, 원자료 미첨부)</t>
-        </is>
-      </c>
-      <c r="G44" s="86" t="n"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>종전 (2022.02 ~ 2026.07)</t>
+        </is>
+      </c>
+      <c r="D44" s="83" t="n"/>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>확대 후 (2026.07.31 ~)</t>
+        </is>
+      </c>
+      <c r="F44" s="83" t="n"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="81" t="n"/>
-      <c r="B45" s="87" t="inlineStr">
-        <is>
-          <t>⚠ 산업 특성</t>
+      <c r="B45" s="84" t="inlineStr">
+        <is>
+          <t>항목명</t>
         </is>
       </c>
       <c r="C45" s="85" t="inlineStr">
         <is>
-          <t>국산 재활로봇 다수가 신의료기술평가에서 '기존기술' 판정을 받아 별도 수가 미확보 → 환자 전액 부담으로 고가 장비 판매 곤란</t>
+          <t>보행치료-뇌졸중 환자에서 로봇을 사용한 보행훈련</t>
         </is>
       </c>
       <c r="D45" s="86" t="n"/>
-      <c r="E45" s="86" t="n"/>
-      <c r="F45" s="80" t="inlineStr">
-        <is>
-          <t>웹 리서치 기반. 공시·증권사 리포트에 근거 없음 — 원문 확인 필요</t>
-        </is>
-      </c>
-      <c r="G45" s="86" t="n"/>
+      <c r="E45" s="85" t="inlineStr">
+        <is>
+          <t>보행치료-뇌졸중 및 18세 이하 뇌성마비 등 중추신경계 질환 환자에 있어서 로봇을 사용한 보행훈련</t>
+        </is>
+      </c>
+      <c r="F45" s="86" t="n"/>
+      <c r="G45" s="80" t="inlineStr">
+        <is>
+          <t>복지부 고시 제2026-166호</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="81" t="n"/>
       <c r="B46" s="84" t="inlineStr">
         <is>
-          <t>정책 방향</t>
+          <t>대상 질환</t>
         </is>
       </c>
       <c r="C46" s="85" t="inlineStr">
         <is>
-          <t>뇌졸중 외 척수손상·파킨슨 등 기타 질환에 대한 치료효과성 입증 시 수가화 추진 (보건복지부)</t>
+          <t>뇌졸중 (상병코드 I60~I64)</t>
         </is>
       </c>
       <c r="D46" s="86" t="n"/>
-      <c r="E46" s="86" t="n"/>
-      <c r="F46" s="80" t="inlineStr">
-        <is>
-          <t>한국IR협의회 기업리서치센터(2024.09.26) (2차)</t>
-        </is>
-      </c>
-      <c r="G46" s="86" t="n"/>
+      <c r="E46" s="85" t="inlineStr">
+        <is>
+          <t>좌동 + 18세 이하 뇌성마비 등 중추신경계 질환</t>
+        </is>
+      </c>
+      <c r="F46" s="86" t="n"/>
+      <c r="G46" s="80" t="inlineStr">
+        <is>
+          <t>심평원 심사기준 / 복지부 고시</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="81" t="n"/>
       <c r="B47" s="84" t="inlineStr">
         <is>
-          <t>상반된 흐름</t>
+          <t>기능 요건</t>
         </is>
       </c>
       <c r="C47" s="85" t="inlineStr">
         <is>
-          <t>'스마트 안전장비 보급확산' 등 정부주도 보급사업의 보조금 감소로 angel GEAR B2G 시장 축소</t>
+          <t>FAC(기능적 보행지수) 2 이하 (0~5단계 기준)</t>
         </is>
       </c>
       <c r="D47" s="86" t="n"/>
-      <c r="E47" s="86" t="n"/>
-      <c r="F47" s="80" t="inlineStr">
-        <is>
-          <t>반기보고서 「예측치 대비 실적 비교」 괴리사유 (2025년·2026년 반기 모두 기재)</t>
-        </is>
-      </c>
-      <c r="G47" s="86" t="n"/>
+      <c r="E47" s="85" t="inlineStr">
+        <is>
+          <t>뇌졸중은 좌동, 소아·청소년은 재활치료 시작 시점 대운동기능 분류단계(GMFCS) 2~4단계</t>
+        </is>
+      </c>
+      <c r="F47" s="86" t="n"/>
+      <c r="G47" s="80" t="inlineStr">
+        <is>
+          <t>심평원 심사기준 / 복지부 고시</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="88" t="inlineStr">
-        <is>
-          <t>주) 엔젤렉스 M20은 2022.12.14 웨어러블 로봇 최초로 의료기기 3등급(로봇보조정형용운동장치) 품목허가를 받아 MM304 적용이 가능해짐 — 반기보고서 연혁·사업의 내용</t>
-        </is>
-      </c>
-      <c r="B48" s="89" t="n"/>
-      <c r="C48" s="90" t="n"/>
-      <c r="D48" s="90" t="n"/>
-      <c r="E48" s="90" t="n"/>
-      <c r="F48" s="90" t="n"/>
-      <c r="G48" s="81" t="n"/>
+      <c r="A48" s="88" t="n"/>
+      <c r="B48" s="84" t="inlineStr">
+        <is>
+          <t>실시 기간</t>
+        </is>
+      </c>
+      <c r="C48" s="85" t="inlineStr">
+        <is>
+          <t>발병 후 6개월까지</t>
+        </is>
+      </c>
+      <c r="D48" s="86" t="n"/>
+      <c r="E48" s="85" t="inlineStr">
+        <is>
+          <t>뇌졸중은 좌동, 소아·청소년은 환자 상황에 따라 적용</t>
+        </is>
+      </c>
+      <c r="F48" s="86" t="n"/>
+      <c r="G48" s="80" t="inlineStr">
+        <is>
+          <t>심평원 심사기준 / 복지부 고시</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="91" t="inlineStr">
-        <is>
-          <t>■ ⚠ 표시 2개 행은 웹 리서치 기반으로 1차 근거가 없음. 외부 배포용 IM 인용 전 반드시 심평원·복지부 고시 원문으로 대조할 것</t>
-        </is>
-      </c>
-      <c r="B49" s="89" t="n"/>
-      <c r="C49" s="90" t="n"/>
-      <c r="D49" s="90" t="n"/>
-      <c r="E49" s="90" t="n"/>
-      <c r="F49" s="90" t="n"/>
-      <c r="G49" s="81" t="n"/>
+      <c r="A49" s="91" t="n"/>
+      <c r="B49" s="84" t="inlineStr">
+        <is>
+          <t>본인부담률</t>
+        </is>
+      </c>
+      <c r="C49" s="85" t="inlineStr">
+        <is>
+          <t>50% (선별급여)</t>
+        </is>
+      </c>
+      <c r="D49" s="86" t="n"/>
+      <c r="E49" s="85" t="inlineStr">
+        <is>
+          <t>50% — 변동 없음</t>
+        </is>
+      </c>
+      <c r="F49" s="86" t="n"/>
+      <c r="G49" s="80" t="inlineStr">
+        <is>
+          <t>복지부 고시 제2026-166호</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="81" t="n"/>
-      <c r="B50" s="89" t="n"/>
-      <c r="C50" s="90" t="n"/>
-      <c r="D50" s="90" t="n"/>
-      <c r="E50" s="90" t="n"/>
-      <c r="F50" s="90" t="n"/>
-      <c r="G50" s="81" t="n"/>
+      <c r="B50" s="84" t="inlineStr">
+        <is>
+          <t>수가 점수</t>
+        </is>
+      </c>
+      <c r="C50" s="85" t="inlineStr">
+        <is>
+          <t>MM302 177.42점 / MM304 317.87점 별도 산정</t>
+        </is>
+      </c>
+      <c r="D50" s="86" t="n"/>
+      <c r="E50" s="85" t="inlineStr">
+        <is>
+          <t>(변동 확인 안 됨)</t>
+        </is>
+      </c>
+      <c r="F50" s="86" t="n"/>
+      <c r="G50" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 인용 행위 급여목록 사-130</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="81" t="n"/>
+      <c r="A51" s="100" t="inlineStr">
+        <is>
+          <t>주) FAC 2 이하·발병 후 6개월 요건은 종전 심평원 심사기준으로 확인됨 (직전 버전에서 '미확인'으로 표기했던 항목을 확정 처리)</t>
+        </is>
+      </c>
       <c r="B51" s="89" t="n"/>
       <c r="C51" s="90" t="n"/>
       <c r="D51" s="90" t="n"/>
@@ -3171,11 +3255,7 @@
     </row>
     <row r="52">
       <c r="A52" s="81" t="n"/>
-      <c r="B52" s="92" t="inlineStr">
-        <is>
-          <t>국내외 경쟁사</t>
-        </is>
-      </c>
+      <c r="B52" s="92" t="n"/>
       <c r="C52" s="90" t="n"/>
       <c r="D52" s="90" t="n"/>
       <c r="E52" s="90" t="n"/>
@@ -3184,232 +3264,200 @@
     </row>
     <row r="53">
       <c r="A53" s="81" t="n"/>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>기업</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>설립/상장</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="F53" s="83" t="n"/>
-      <c r="G53" s="83" t="n"/>
+      <c r="B53" s="101" t="n"/>
+      <c r="C53" s="101" t="n"/>
+      <c r="D53" s="101" t="n"/>
+      <c r="E53" s="101" t="n"/>
+      <c r="F53" s="81" t="n"/>
+      <c r="G53" s="81" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="81" t="n"/>
-      <c r="B54" s="84" t="inlineStr">
-        <is>
-          <t>국내 상장</t>
-        </is>
-      </c>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>피앤에스로보틱스 (460940)</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>2003년 설립 / 2024.07 상장</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>보행재활훈련 로봇 Walkbot — 트레드밀 기반 고정형, 해외매출 비중 높음 (동사와 제품 형태·시장 상이)</t>
-        </is>
-      </c>
-      <c r="F54" s="86" t="n"/>
-      <c r="G54" s="86" t="n"/>
+      <c r="B54" s="99" t="inlineStr">
+        <is>
+          <t>수가 체계 ③ 급여 확대의 근거·함의·향후</t>
+        </is>
+      </c>
+      <c r="C54" s="96" t="n"/>
+      <c r="D54" s="96" t="n"/>
+      <c r="E54" s="96" t="n"/>
+      <c r="F54" s="81" t="n"/>
+      <c r="G54" s="81" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="88" t="n"/>
-      <c r="B55" s="84" t="inlineStr">
-        <is>
-          <t>국내 비상장</t>
-        </is>
-      </c>
-      <c r="C55" s="85" t="inlineStr">
-        <is>
-          <t>FRT로보틱스</t>
-        </is>
-      </c>
-      <c r="D55" s="85" t="inlineStr">
-        <is>
-          <t>2015년</t>
-        </is>
-      </c>
-      <c r="E55" s="85" t="inlineStr">
-        <is>
-          <t>웨어러블 로봇</t>
-        </is>
-      </c>
-      <c r="F55" s="86" t="n"/>
-      <c r="G55" s="86" t="n"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D55" s="83" t="n"/>
+      <c r="E55" s="83" t="n"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>출처 (행별)</t>
+        </is>
+      </c>
+      <c r="G55" s="83" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="81" t="n"/>
-      <c r="B56" s="84" t="inlineStr">
-        <is>
-          <t>국내 비상장</t>
+      <c r="B56" s="94" t="inlineStr">
+        <is>
+          <t>임상 근거</t>
         </is>
       </c>
       <c r="C56" s="85" t="inlineStr">
         <is>
-          <t>헥사휴먼케어</t>
-        </is>
-      </c>
-      <c r="D56" s="85" t="inlineStr">
-        <is>
-          <t>2016년</t>
-        </is>
-      </c>
-      <c r="E56" s="85" t="inlineStr">
-        <is>
-          <t>웨어러블 로봇</t>
-        </is>
-      </c>
-      <c r="F56" s="86" t="n"/>
+          <t>2024년 뇌성마비 아동 90명 대상 연구에서 로봇보조 보행훈련군이 물리치료 대조군 대비 대운동기능·균형조절·보행패턴에서 유의미한 향상. 동 연구는 동사가 5개 의료기관과 수행하여 JAMA Network Open에 게재한 논문</t>
+        </is>
+      </c>
+      <c r="D56" s="86" t="n"/>
+      <c r="E56" s="86" t="n"/>
+      <c r="F56" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 연혁·사업의 내용 + 급여 확대 보도 (임상↔급여확대 연결은 언론 보도 기준)</t>
+        </is>
+      </c>
       <c r="G56" s="86" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="81" t="n"/>
       <c r="B57" s="84" t="inlineStr">
         <is>
-          <t>국내 비상장</t>
+          <t>수요 모수</t>
         </is>
       </c>
       <c r="C57" s="85" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
-        </is>
-      </c>
-      <c r="D57" s="85" t="inlineStr">
-        <is>
-          <t>2016년</t>
-        </is>
-      </c>
-      <c r="E57" s="85" t="inlineStr">
-        <is>
-          <t>웨어러블 로봇</t>
-        </is>
-      </c>
-      <c r="F57" s="86" t="n"/>
+          <t>소아 뇌성마비 환자 약 8만명 — 종전 급여 대상 외였던 모집단이 급여권으로 편입</t>
+        </is>
+      </c>
+      <c r="D57" s="86" t="n"/>
+      <c r="E57" s="86" t="n"/>
+      <c r="F57" s="80" t="inlineStr">
+        <is>
+          <t>엔젤로보틱스 IR Book / 유진투자증권 (2차, 2024년 기준)</t>
+        </is>
+      </c>
       <c r="G57" s="86" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="81" t="n"/>
-      <c r="B58" s="84" t="inlineStr">
-        <is>
-          <t>해외 상장</t>
+      <c r="B58" s="87" t="inlineStr">
+        <is>
+          <t>⚠ 경쟁 영향</t>
         </is>
       </c>
       <c r="C58" s="85" t="inlineStr">
         <is>
-          <t>라이프워드 (구 리워크, 나스닥)</t>
-        </is>
-      </c>
-      <c r="D58" s="85" t="inlineStr">
-        <is>
-          <t>이스라엘</t>
-        </is>
-      </c>
-      <c r="E58" s="85" t="inlineStr">
-        <is>
-          <t>2014.06 FDA 하지 외골격로봇 허가</t>
-        </is>
-      </c>
-      <c r="F58" s="86" t="n"/>
+          <t>코스모로보틱스 '밤비니 틴즈 프로'도 동일 급여 확대의 수혜 대상. 동사 단독 호재가 아니며, 동사는 '밤비니 키즈'로 소아 전용 라인 급여 편입도 추진 중</t>
+        </is>
+      </c>
+      <c r="D58" s="86" t="n"/>
+      <c r="E58" s="86" t="n"/>
+      <c r="F58" s="80" t="inlineStr">
+        <is>
+          <t>로봇신문 (2026) — 인용 시 원문 확인 필요</t>
+        </is>
+      </c>
       <c r="G58" s="86" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="81" t="n"/>
       <c r="B59" s="84" t="inlineStr">
         <is>
-          <t>해외 상장</t>
+          <t>향후 적응증</t>
         </is>
       </c>
       <c r="C59" s="85" t="inlineStr">
         <is>
-          <t>Ekso Bionics (나스닥)</t>
-        </is>
-      </c>
-      <c r="D59" s="85" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="E59" s="85" t="inlineStr">
-        <is>
-          <t>Ekso GT 척수손상·뇌졸중 FDA 허가</t>
-        </is>
-      </c>
-      <c r="F59" s="86" t="n"/>
+          <t>뇌졸중 외 척수손상·파킨슨병·뇌종양 등에서도 재활효과가 확인되고 있으며, 치료효과성 입증 시 수가화 추진 방침</t>
+        </is>
+      </c>
+      <c r="D59" s="86" t="n"/>
+      <c r="E59" s="86" t="n"/>
+      <c r="F59" s="80" t="inlineStr">
+        <is>
+          <t>한국IR협의회(2024.09.26) + 언론 보도 (구체적 일정·대상 미확정)</t>
+        </is>
+      </c>
       <c r="G59" s="86" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="81" t="n"/>
-      <c r="B60" s="84" t="inlineStr">
-        <is>
-          <t>해외</t>
+      <c r="B60" s="87" t="inlineStr">
+        <is>
+          <t>⚠ 재평가 리스크</t>
         </is>
       </c>
       <c r="C60" s="85" t="inlineStr">
         <is>
-          <t>사이버다인</t>
-        </is>
-      </c>
-      <c r="D60" s="85" t="inlineStr">
-        <is>
-          <t>일본</t>
-        </is>
-      </c>
-      <c r="E60" s="85" t="inlineStr">
-        <is>
-          <t>HAL 시리즈 — 생체신호(근전도) 센서 사용, 탈의 후 피부 부착 방식</t>
-        </is>
-      </c>
-      <c r="F60" s="86" t="n"/>
+          <t>선별급여 평가주기 5년 → 2022.02 신설 기준 2027년 적합성 재평가 도래 추정. 재평가 결과에 따라 급여 지속·본인부담률 조정 가능</t>
+        </is>
+      </c>
+      <c r="D60" s="86" t="n"/>
+      <c r="E60" s="86" t="n"/>
+      <c r="F60" s="80" t="inlineStr">
+        <is>
+          <t>평가주기 5년은 고시 확인 사항. 2027년 도래는 이로부터의 추정이며 재평가 일정 자체는 미확인</t>
+        </is>
+      </c>
       <c r="G60" s="86" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="88" t="inlineStr">
-        <is>
-          <t>출처: 반기보고서 「경쟁 현황 및 비교우위 사항」, 한국IR협의회(2024.09.26), 리딩투자증권(2025.12.16)</t>
-        </is>
-      </c>
-      <c r="B61" s="81" t="n"/>
-      <c r="C61" s="81" t="n"/>
-      <c r="D61" s="81" t="n"/>
-      <c r="E61" s="81" t="n"/>
-      <c r="F61" s="81" t="n"/>
-      <c r="G61" s="81" t="n"/>
+      <c r="A61" s="88" t="n"/>
+      <c r="B61" s="87" t="inlineStr">
+        <is>
+          <t>⚠ 산업 특성</t>
+        </is>
+      </c>
+      <c r="C61" s="85" t="inlineStr">
+        <is>
+          <t>국산 재활로봇 다수가 신의료기술평가에서 '기존기술' 판정을 받아 별도 수가 미확보 → 환자 전액 부담으로 고가 장비 판매 곤란</t>
+        </is>
+      </c>
+      <c r="D61" s="86" t="n"/>
+      <c r="E61" s="86" t="n"/>
+      <c r="F61" s="80" t="inlineStr">
+        <is>
+          <t>웹 리서치 기반. 공시·증권사 리포트에 근거 없음 — NECA 신의료기술평가 공고로 확인 필요</t>
+        </is>
+      </c>
+      <c r="G61" s="86" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="88" t="inlineStr">
-        <is>
-          <t>참고) 세브란스 재활병원은 7개 재활로봇을 보유하고 보행재활을 5단계로 운영하며, 엔젤렉스는 회복이 가장 진행된 5단계에 배치 — 한국IR협의회</t>
-        </is>
-      </c>
-      <c r="B62" s="81" t="n"/>
-      <c r="C62" s="81" t="n"/>
-      <c r="D62" s="81" t="n"/>
-      <c r="E62" s="81" t="n"/>
-      <c r="F62" s="81" t="n"/>
-      <c r="G62" s="81" t="n"/>
+      <c r="A62" s="88" t="n"/>
+      <c r="B62" s="84" t="inlineStr">
+        <is>
+          <t>상반된 흐름</t>
+        </is>
+      </c>
+      <c r="C62" s="85" t="inlineStr">
+        <is>
+          <t>'스마트 안전장비 보급확산' 등 정부주도 보급사업의 보조금 감소로 angel GEAR의 B2G 시장은 축소</t>
+        </is>
+      </c>
+      <c r="D62" s="86" t="n"/>
+      <c r="E62" s="86" t="n"/>
+      <c r="F62" s="80" t="inlineStr">
+        <is>
+          <t>반기보고서 「예측치 대비 실적 비교」 괴리사유 (2025년·2026년 반기 모두 기재)</t>
+        </is>
+      </c>
+      <c r="G62" s="86" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="81" t="n"/>
+      <c r="A63" s="91" t="inlineStr">
+        <is>
+          <t>■ 초록색 = 반기보고서 기준일 이후 확보한 신규 사실 / 붉은색 ⚠ = 1차 근거 미확보 또는 추정. 외부 배포용 IM 인용 전 원문 대조 필요</t>
+        </is>
+      </c>
       <c r="B63" s="81" t="n"/>
       <c r="C63" s="81" t="n"/>
       <c r="D63" s="81" t="n"/>
@@ -3437,7 +3485,11 @@
     </row>
     <row r="66">
       <c r="A66" s="81" t="n"/>
-      <c r="B66" s="81" t="n"/>
+      <c r="B66" s="82" t="inlineStr">
+        <is>
+          <t>국내외 경쟁사</t>
+        </is>
+      </c>
       <c r="C66" s="81" t="n"/>
       <c r="D66" s="81" t="n"/>
       <c r="E66" s="81" t="n"/>
@@ -3446,63 +3498,399 @@
     </row>
     <row r="67">
       <c r="A67" s="81" t="n"/>
-      <c r="B67" s="81" t="n"/>
-      <c r="C67" s="81" t="n"/>
-      <c r="D67" s="81" t="n"/>
-      <c r="E67" s="81" t="n"/>
-      <c r="F67" s="81" t="n"/>
-      <c r="G67" s="81" t="n"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>기업</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>설립/상장</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="F67" s="83" t="n"/>
+      <c r="G67" s="83" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="81" t="n"/>
-      <c r="B68" s="81" t="n"/>
-      <c r="C68" s="81" t="n"/>
-      <c r="D68" s="81" t="n"/>
-      <c r="E68" s="81" t="n"/>
-      <c r="F68" s="81" t="n"/>
-      <c r="G68" s="81" t="n"/>
+      <c r="B68" s="94" t="inlineStr">
+        <is>
+          <t>국내 상장</t>
+        </is>
+      </c>
+      <c r="C68" s="85" t="inlineStr">
+        <is>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="D68" s="85" t="inlineStr">
+        <is>
+          <t>2016년 설립 / 2026.05.11 상장</t>
+        </is>
+      </c>
+      <c r="E68" s="85" t="inlineStr">
+        <is>
+          <t>뇌졸중·뇌성마비·척수손상 보행재활 웨어러블 로봇. 공모가 6,000원, 상장 후 3거래일 연속 상한가, 시가총액 1.3조원 상회. 일반청약 경쟁률 2,013.8:1(증거금 6.3조원), 공모자금 약 250억원. 밤비니 틴즈 프로가 2026.07 급여 확대 수혜</t>
+        </is>
+      </c>
+      <c r="F68" s="86" t="n"/>
+      <c r="G68" s="86" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="81" t="n"/>
-      <c r="B69" s="81" t="n"/>
-      <c r="C69" s="81" t="n"/>
-      <c r="D69" s="81" t="n"/>
-      <c r="E69" s="81" t="n"/>
-      <c r="F69" s="81" t="n"/>
-      <c r="G69" s="81" t="n"/>
+      <c r="B69" s="84" t="inlineStr">
+        <is>
+          <t>국내 상장</t>
+        </is>
+      </c>
+      <c r="C69" s="85" t="inlineStr">
+        <is>
+          <t>피앤에스로보틱스 (460940)</t>
+        </is>
+      </c>
+      <c r="D69" s="85" t="inlineStr">
+        <is>
+          <t>2003년 설립 / 2024.07 상장</t>
+        </is>
+      </c>
+      <c r="E69" s="85" t="inlineStr">
+        <is>
+          <t>보행재활훈련 로봇 Walkbot — 트레드밀 기반 고정형, 해외매출 비중 높음 (동사와 제품 형태·시장 상이)</t>
+        </is>
+      </c>
+      <c r="F69" s="86" t="n"/>
+      <c r="G69" s="86" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="81" t="n"/>
+      <c r="B70" s="84" t="inlineStr">
+        <is>
+          <t>국내 비상장</t>
+        </is>
+      </c>
+      <c r="C70" s="85" t="inlineStr">
+        <is>
+          <t>FRT로보틱스</t>
+        </is>
+      </c>
+      <c r="D70" s="85" t="inlineStr">
+        <is>
+          <t>2015년</t>
+        </is>
+      </c>
+      <c r="E70" s="85" t="inlineStr">
+        <is>
+          <t>웨어러블 로봇</t>
+        </is>
+      </c>
+      <c r="F70" s="86" t="n"/>
+      <c r="G70" s="86" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="81" t="n"/>
+      <c r="B71" s="84" t="inlineStr">
+        <is>
+          <t>국내 비상장</t>
+        </is>
+      </c>
+      <c r="C71" s="85" t="inlineStr">
+        <is>
+          <t>헥사휴먼케어</t>
+        </is>
+      </c>
+      <c r="D71" s="85" t="inlineStr">
+        <is>
+          <t>2016년</t>
+        </is>
+      </c>
+      <c r="E71" s="85" t="inlineStr">
+        <is>
+          <t>웨어러블 로봇</t>
+        </is>
+      </c>
+      <c r="F71" s="86" t="n"/>
+      <c r="G71" s="86" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="81" t="n"/>
+      <c r="B72" s="84" t="inlineStr">
+        <is>
+          <t>해외 상장</t>
+        </is>
+      </c>
+      <c r="C72" s="85" t="inlineStr">
+        <is>
+          <t>라이프워드 (구 리워크, 나스닥)</t>
+        </is>
+      </c>
+      <c r="D72" s="85" t="inlineStr">
+        <is>
+          <t>이스라엘</t>
+        </is>
+      </c>
+      <c r="E72" s="85" t="inlineStr">
+        <is>
+          <t>2014.06 FDA 하지 외골격로봇 허가</t>
+        </is>
+      </c>
+      <c r="F72" s="86" t="n"/>
+      <c r="G72" s="86" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="81" t="n"/>
+      <c r="B73" s="84" t="inlineStr">
+        <is>
+          <t>해외 상장</t>
+        </is>
+      </c>
+      <c r="C73" s="85" t="inlineStr">
+        <is>
+          <t>Ekso Bionics (나스닥)</t>
+        </is>
+      </c>
+      <c r="D73" s="85" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="E73" s="85" t="inlineStr">
+        <is>
+          <t>Ekso GT 척수손상·뇌졸중 FDA 허가</t>
+        </is>
+      </c>
+      <c r="F73" s="86" t="n"/>
+      <c r="G73" s="86" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="81" t="n"/>
+      <c r="B74" s="84" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C74" s="85" t="inlineStr">
+        <is>
+          <t>사이버다인</t>
+        </is>
+      </c>
+      <c r="D74" s="85" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="E74" s="85" t="inlineStr">
+        <is>
+          <t>HAL 시리즈 — 생체신호(근전도) 센서 사용, 탈의 후 피부 부착 방식</t>
+        </is>
+      </c>
+      <c r="F74" s="86" t="n"/>
+      <c r="G74" s="86" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="88" t="inlineStr">
+        <is>
+          <t>출처: 반기보고서 「경쟁 현황 및 비교우위 사항」, 한국IR협의회(2024.09.26), 리딩투자증권(2025.12.16), 코스모로보틱스 상장 관련 언론 보도(2026.05)</t>
+        </is>
+      </c>
+      <c r="B75" s="81" t="n"/>
+      <c r="C75" s="81" t="n"/>
+      <c r="D75" s="81" t="n"/>
+      <c r="E75" s="81" t="n"/>
+      <c r="F75" s="81" t="n"/>
+      <c r="G75" s="81" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="91" t="inlineStr">
+        <is>
+          <t>⚠ 코스모로보틱스는 2026.05 상장한 직접 경쟁사로, 밸류에이션 비교군이자 소아 재활 시장의 경쟁 요인. 11_주가·밸류에이션 시트에 미반영 상태</t>
+        </is>
+      </c>
+      <c r="B76" s="81" t="n"/>
+      <c r="C76" s="81" t="n"/>
+      <c r="D76" s="81" t="n"/>
+      <c r="E76" s="81" t="n"/>
+      <c r="F76" s="81" t="n"/>
+      <c r="G76" s="81" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="88" t="inlineStr">
+        <is>
+          <t>참고) 세브란스 재활병원은 7개 재활로봇을 보유하고 보행재활을 5단계로 운영하며, 엔젤렉스는 회복이 가장 진행된 5단계에 배치 — 한국IR협의회</t>
+        </is>
+      </c>
+      <c r="B77" s="81" t="n"/>
+      <c r="C77" s="81" t="n"/>
+      <c r="D77" s="81" t="n"/>
+      <c r="E77" s="81" t="n"/>
+      <c r="F77" s="81" t="n"/>
+      <c r="G77" s="81" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="81" t="n"/>
+      <c r="B78" s="81" t="n"/>
+      <c r="C78" s="81" t="n"/>
+      <c r="D78" s="81" t="n"/>
+      <c r="E78" s="81" t="n"/>
+      <c r="F78" s="81" t="n"/>
+      <c r="G78" s="81" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="81" t="n"/>
+      <c r="B79" s="81" t="n"/>
+      <c r="C79" s="81" t="n"/>
+      <c r="D79" s="81" t="n"/>
+      <c r="E79" s="81" t="n"/>
+      <c r="F79" s="81" t="n"/>
+      <c r="G79" s="81" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="81" t="n"/>
+      <c r="B80" s="81" t="n"/>
+      <c r="C80" s="81" t="n"/>
+      <c r="D80" s="81" t="n"/>
+      <c r="E80" s="81" t="n"/>
+      <c r="F80" s="81" t="n"/>
+      <c r="G80" s="81" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="81" t="n"/>
+      <c r="B81" s="81" t="n"/>
+      <c r="C81" s="81" t="n"/>
+      <c r="D81" s="81" t="n"/>
+      <c r="E81" s="81" t="n"/>
+      <c r="F81" s="81" t="n"/>
+      <c r="G81" s="81" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="81" t="n"/>
+      <c r="B82" s="81" t="n"/>
+      <c r="C82" s="81" t="n"/>
+      <c r="D82" s="81" t="n"/>
+      <c r="E82" s="81" t="n"/>
+      <c r="F82" s="81" t="n"/>
+      <c r="G82" s="81" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="81" t="n"/>
+      <c r="B83" s="81" t="n"/>
+      <c r="C83" s="81" t="n"/>
+      <c r="D83" s="81" t="n"/>
+      <c r="E83" s="81" t="n"/>
+      <c r="F83" s="81" t="n"/>
+      <c r="G83" s="81" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="81" t="n"/>
+      <c r="B84" s="81" t="n"/>
+      <c r="C84" s="81" t="n"/>
+      <c r="D84" s="81" t="n"/>
+      <c r="E84" s="81" t="n"/>
+      <c r="F84" s="81" t="n"/>
+      <c r="G84" s="81" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="81" t="n"/>
+      <c r="B85" s="81" t="n"/>
+      <c r="C85" s="81" t="n"/>
+      <c r="D85" s="81" t="n"/>
+      <c r="E85" s="81" t="n"/>
+      <c r="F85" s="81" t="n"/>
+      <c r="G85" s="81" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="81" t="n"/>
+      <c r="B86" s="81" t="n"/>
+      <c r="C86" s="81" t="n"/>
+      <c r="D86" s="81" t="n"/>
+      <c r="E86" s="81" t="n"/>
+      <c r="F86" s="81" t="n"/>
+      <c r="G86" s="81" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="81" t="n"/>
+      <c r="B87" s="81" t="n"/>
+      <c r="C87" s="81" t="n"/>
+      <c r="D87" s="81" t="n"/>
+      <c r="E87" s="81" t="n"/>
+      <c r="F87" s="81" t="n"/>
+      <c r="G87" s="81" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="81" t="n"/>
+      <c r="B88" s="81" t="n"/>
+      <c r="C88" s="81" t="n"/>
+      <c r="D88" s="81" t="n"/>
+      <c r="E88" s="81" t="n"/>
+      <c r="F88" s="81" t="n"/>
+      <c r="G88" s="81" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="81" t="n"/>
+      <c r="B89" s="81" t="n"/>
+      <c r="C89" s="81" t="n"/>
+      <c r="D89" s="81" t="n"/>
+      <c r="E89" s="81" t="n"/>
+      <c r="F89" s="81" t="n"/>
+      <c r="G89" s="81" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="E60:G60"/>
+  <mergeCells count="46">
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="E69:G69"/>
     <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="C59:E59"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C61:E61"/>
     <mergeCell ref="C39:E39"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E70:G70"/>
     <mergeCell ref="C38:E38"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="F38:G38"/>
     <mergeCell ref="C37:E37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -4629,7 +5017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F45"/>
+  <dimension ref="A2:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5156,178 +5544,313 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" s="102" t="inlineStr">
+        <is>
+          <t>로봇 보행훈련 급여 확대 고시 제2026-166호</t>
+        </is>
+      </c>
+      <c r="C32" s="85" t="inlineStr">
+        <is>
+          <t>보건복지부 훈령/예규/고시</t>
+        </is>
+      </c>
+      <c r="D32" s="85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E32" s="85" t="inlineStr">
+        <is>
+          <t>https://mohw.go.kr/board.es?act=view&amp;bid=0026&amp;list_no=1491480&amp;mid=a10409020000</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="66" t="inlineStr">
+      <c r="B33" s="102" t="inlineStr">
+        <is>
+          <t>급여 확대 상세 (18세 이하 뇌성마비, GMFCS 2~4단계)</t>
+        </is>
+      </c>
+      <c r="C33" s="85" t="inlineStr">
+        <is>
+          <t>의약일보</t>
+        </is>
+      </c>
+      <c r="D33" s="85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="85" t="inlineStr">
+        <is>
+          <t>https://www.medicaldaily.co.kr/post/21588</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="102" t="inlineStr">
+        <is>
+          <t>엔젤렉스 M20 급여 확대 보도</t>
+        </is>
+      </c>
+      <c r="C34" s="85" t="inlineStr">
+        <is>
+          <t>ZDNet Korea</t>
+        </is>
+      </c>
+      <c r="D34" s="85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E34" s="85" t="inlineStr">
+        <is>
+          <t>https://zdnet.co.kr/view/?no=20260803083607</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="102" t="inlineStr">
+        <is>
+          <t>종전 급여기준 (뇌졸중 I60~I64, FAC 2 이하, 발병 후 6개월)</t>
+        </is>
+      </c>
+      <c r="C35" s="85" t="inlineStr">
+        <is>
+          <t>건강보험심사평가원 심사기준조회</t>
+        </is>
+      </c>
+      <c r="D35" s="85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="85" t="inlineStr">
+        <is>
+          <t>https://m.hira.or.kr/mobile/rf/iac/eva/data.do?openDT=20220201&amp;seqNO=4&amp;matrSeqNo=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="102" t="inlineStr">
+        <is>
+          <t>코스모로보틱스 밤비니 틴즈 프로 급여 확대</t>
+        </is>
+      </c>
+      <c r="C36" s="85" t="inlineStr">
+        <is>
+          <t>로봇신문</t>
+        </is>
+      </c>
+      <c r="D36" s="85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E36" s="85" t="inlineStr">
+        <is>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47963</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="102" t="inlineStr">
+        <is>
+          <t>엔젤슈트 H10 베트남 의료기기 등록 (2026.08.05)</t>
+        </is>
+      </c>
+      <c r="C37" s="85" t="inlineStr">
+        <is>
+          <t>ZDNet Korea / 로봇신문</t>
+        </is>
+      </c>
+      <c r="D37" s="85" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E37" s="85" t="inlineStr">
+        <is>
+          <t>https://zdnet.co.kr/view/?no=20260805083950</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="66" t="inlineStr">
         <is>
           <t>주1) 웹 소스는 검색 결과 요약을 기반으로 하며, 본문 인용 시 원문 확인이 필요함</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>주2) DART·증권사·통계 사이트는 현재 작업 환경에서 직접 접속이 제한되어 1차 자료는 파일 업로드로 확보</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="79" t="inlineStr">
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>미확보 항목 (발행사 확보 필요)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>영향 범위</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="63" t="inlineStr">
-        <is>
-          <t>딜 조건 (규모·만기·금리·옵션)</t>
-        </is>
-      </c>
-      <c r="C39" s="53" t="inlineStr">
-        <is>
-          <t>Term Sheet 전체</t>
-        </is>
-      </c>
-      <c r="D39" s="53" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="E39" s="53" t="inlineStr"/>
-      <c r="F39" s="53" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="63" t="inlineStr">
-        <is>
-          <t>CPS 자본분류 감사인 의견</t>
-        </is>
-      </c>
-      <c r="C40" s="53" t="inlineStr">
-        <is>
-          <t>12_시뮬레이션 전제</t>
-        </is>
-      </c>
-      <c r="D40" s="53" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="E40" s="53" t="inlineStr"/>
-      <c r="F40" s="53" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="63" t="inlineStr">
-        <is>
-          <t>아세안 수주 파이프라인</t>
-        </is>
-      </c>
-      <c r="C41" s="53" t="inlineStr">
-        <is>
-          <t>해외 매출 논거</t>
-        </is>
-      </c>
-      <c r="D41" s="53" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="E41" s="53" t="inlineStr"/>
-      <c r="F41" s="53" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="63" t="inlineStr">
-        <is>
-          <t>BEP 매출 규모</t>
-        </is>
-      </c>
-      <c r="C42" s="53" t="inlineStr">
-        <is>
-          <t>영업레버리지 논거</t>
-        </is>
-      </c>
-      <c r="D42" s="53" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="E42" s="53" t="inlineStr"/>
-      <c r="F42" s="53" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="63" t="inlineStr">
-        <is>
-          <t>제품별 마진</t>
-        </is>
-      </c>
-      <c r="C43" s="53" t="inlineStr">
-        <is>
-          <t>06_제품별매출</t>
-        </is>
-      </c>
-      <c r="D43" s="53" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="E43" s="53" t="inlineStr"/>
-      <c r="F43" s="53" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="63" t="inlineStr">
-        <is>
-          <t>경쟁사 실명 및 최신 점유율</t>
-        </is>
-      </c>
-      <c r="C44" s="53" t="inlineStr">
-        <is>
-          <t>10_시장·산업</t>
-        </is>
-      </c>
-      <c r="D44" s="53" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="E44" s="53" t="inlineStr"/>
-      <c r="F44" s="53" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="63" t="inlineStr">
         <is>
-          <t>침투율 최신화 (현재 2023년 기준)</t>
+          <t>딜 조건 (규모·만기·금리·옵션)</t>
         </is>
       </c>
       <c r="C45" s="53" t="inlineStr">
         <is>
-          <t>10_시장·산업</t>
+          <t>Term Sheet 전체</t>
         </is>
       </c>
       <c r="D45" s="53" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E45" s="53" t="inlineStr"/>
       <c r="F45" s="53" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>CPS 자본분류 감사인 의견</t>
+        </is>
+      </c>
+      <c r="C46" s="53" t="inlineStr">
+        <is>
+          <t>12_시뮬레이션 전제</t>
+        </is>
+      </c>
+      <c r="D46" s="53" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="E46" s="53" t="inlineStr"/>
+      <c r="F46" s="53" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>아세안 수주 파이프라인</t>
+        </is>
+      </c>
+      <c r="C47" s="53" t="inlineStr">
+        <is>
+          <t>해외 매출 논거</t>
+        </is>
+      </c>
+      <c r="D47" s="53" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="E47" s="53" t="inlineStr"/>
+      <c r="F47" s="53" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="63" t="inlineStr">
+        <is>
+          <t>BEP 매출 규모</t>
+        </is>
+      </c>
+      <c r="C48" s="53" t="inlineStr">
+        <is>
+          <t>영업레버리지 논거</t>
+        </is>
+      </c>
+      <c r="D48" s="53" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="E48" s="53" t="inlineStr"/>
+      <c r="F48" s="53" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>제품별 마진</t>
+        </is>
+      </c>
+      <c r="C49" s="53" t="inlineStr">
+        <is>
+          <t>06_제품별매출</t>
+        </is>
+      </c>
+      <c r="D49" s="53" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="E49" s="53" t="inlineStr"/>
+      <c r="F49" s="53" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>경쟁사 실명 및 최신 점유율</t>
+        </is>
+      </c>
+      <c r="C50" s="53" t="inlineStr">
+        <is>
+          <t>10_시장·산업</t>
+        </is>
+      </c>
+      <c r="D50" s="53" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="E50" s="53" t="inlineStr"/>
+      <c r="F50" s="53" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>침투율 최신화 (현재 2023년 기준)</t>
+        </is>
+      </c>
+      <c r="C51" s="53" t="inlineStr">
+        <is>
+          <t>10_시장·산업</t>
+        </is>
+      </c>
+      <c r="D51" s="53" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="E51" s="53" t="inlineStr"/>
+      <c r="F51" s="53" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
